--- a/artfynd/A 36107-2026 artfynd.xlsx
+++ b/artfynd/A 36107-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373262</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373278</v>
       </c>
       <c r="B3" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373260</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373249</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373284</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373263</v>
       </c>
       <c r="B7" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 36107-2026 artfynd.xlsx
+++ b/artfynd/A 36107-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373262</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373278</v>
       </c>
       <c r="B3" t="n">
-        <v>92737</v>
+        <v>92742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373260</v>
       </c>
       <c r="B4" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373249</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373284</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373263</v>
       </c>
       <c r="B7" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373251</v>
       </c>
       <c r="B8" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373277</v>
       </c>
       <c r="B9" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373252</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137373264</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137373268</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137373250</v>
       </c>
       <c r="B13" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>137373253</v>
       </c>
       <c r="B14" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>137373254</v>
       </c>
       <c r="B15" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137373256</v>
       </c>
       <c r="B16" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137373257</v>
       </c>
       <c r="B17" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>137373265</v>
       </c>
       <c r="B18" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>137373255</v>
       </c>
       <c r="B19" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137373259</v>
       </c>
       <c r="B20" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>137373266</v>
       </c>
       <c r="B21" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>137373269</v>
       </c>
       <c r="B22" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 36107-2026 artfynd.xlsx
+++ b/artfynd/A 36107-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373262</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373278</v>
       </c>
       <c r="B3" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373260</v>
       </c>
       <c r="B4" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373249</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373284</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373263</v>
       </c>
       <c r="B7" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373251</v>
       </c>
       <c r="B8" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373277</v>
       </c>
       <c r="B9" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373252</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137373264</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137373268</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137373250</v>
       </c>
       <c r="B13" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>137373253</v>
       </c>
       <c r="B14" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>137373254</v>
       </c>
       <c r="B15" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137373256</v>
       </c>
       <c r="B16" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137373257</v>
       </c>
       <c r="B17" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>137373265</v>
       </c>
       <c r="B18" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36107-2026 artfynd.xlsx
+++ b/artfynd/A 36107-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373262</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373278</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373260</v>
       </c>
       <c r="B4" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373249</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373284</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373263</v>
       </c>
       <c r="B7" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373251</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373277</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373252</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137373264</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137373268</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137373250</v>
       </c>
       <c r="B13" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>137373253</v>
       </c>
       <c r="B14" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>137373254</v>
       </c>
       <c r="B15" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137373256</v>
       </c>
       <c r="B16" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137373257</v>
       </c>
       <c r="B17" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>137373265</v>
       </c>
       <c r="B18" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36107-2026 artfynd.xlsx
+++ b/artfynd/A 36107-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373262</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373278</v>
       </c>
       <c r="B3" t="n">
-        <v>92755</v>
+        <v>92758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373260</v>
       </c>
       <c r="B4" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373249</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373284</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373263</v>
       </c>
       <c r="B7" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373251</v>
       </c>
       <c r="B8" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373277</v>
       </c>
       <c r="B9" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373252</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137373264</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137373268</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137373250</v>
       </c>
       <c r="B13" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>137373253</v>
       </c>
       <c r="B14" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>137373254</v>
       </c>
       <c r="B15" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137373256</v>
       </c>
       <c r="B16" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137373257</v>
       </c>
       <c r="B17" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>137373265</v>
       </c>
       <c r="B18" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 36107-2026 artfynd.xlsx
+++ b/artfynd/A 36107-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137373262</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137373278</v>
       </c>
       <c r="B3" t="n">
-        <v>92758</v>
+        <v>92762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137373260</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137373249</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137373284</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137373263</v>
       </c>
       <c r="B7" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137373251</v>
       </c>
       <c r="B8" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137373277</v>
       </c>
       <c r="B9" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137373252</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>137373264</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137373268</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137373250</v>
       </c>
       <c r="B13" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>137373253</v>
       </c>
       <c r="B14" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>137373254</v>
       </c>
       <c r="B15" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>137373256</v>
       </c>
       <c r="B16" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>137373257</v>
       </c>
       <c r="B17" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>137373265</v>
       </c>
       <c r="B18" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>137373255</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>137373259</v>
       </c>
       <c r="B20" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>137373266</v>
       </c>
       <c r="B21" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>137373269</v>
       </c>
       <c r="B22" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
